--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3134,6 +3134,6802 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129357119</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>419347</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6787070</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129357114</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>419458</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6787193</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129357127</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>419531</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6786974</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129357115</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>419460</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6787130</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129357038</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>419467</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6787120</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129367678</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>419262</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6787031</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129357096</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>419433</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6786954</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129357110</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>419465</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6787134</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129357129</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>419416</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6787118</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129357111</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>419456</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6787149</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129357107</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>419474</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6787100</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129357106</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>419505</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6787037</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129357125</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>419485</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6786929</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129357123</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>419467</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6787011</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129357105</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>419505</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6787028</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129357091</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>419411</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6786979</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129367674</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>419339</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6787087</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129364483</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>419459</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6786999</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129357109</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>419470</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6787115</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129357095</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>419457</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6786992</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129367675</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>419314</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6787092</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129357100</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>419525</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6787008</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129357113</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>419460</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6787178</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129367681</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>419245</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6787037</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129367679</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>419258</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6787042</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129364495</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>419475</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6787178</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129364491</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>419450</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6787079</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129364472</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>419439</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6786970</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129367652</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>419265</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6787047</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129367619</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78799</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>419457</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6787086</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129367668</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>419481</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6787056</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129367607</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79631</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>419451</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6787144</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129367657</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>419454</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6787097</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129364497</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>419476</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6787193</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129357103</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>419509</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6787026</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129357092</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>419418</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6786979</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129367666</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>419496</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6787020</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129367680</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>419248</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6787041</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129357121</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>419244</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6787051</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129357126</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>419522</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6786923</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129367669</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>419463</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6787067</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129367663</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>419353</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6787020</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129367676</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>419277</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6787033</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129367656</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>419497</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6787027</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129367655</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>419317</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6787029</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129367664</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>419363</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6787023</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129367651</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>419250</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6787043</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129367653</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>419288</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6787048</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129357094</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>419463</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6786985</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129364493</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>419438</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6787138</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129357120</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>419248</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6787063</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129357117</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>419364</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6787091</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129357118</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>419355</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6787091</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129357099</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>419529</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6786987</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129367658</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>419264</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6787033</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129367677</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>419273</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6787038</v>
+      </c>
+      <c r="S80" t="n">
+        <v>25</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129367673</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>419374</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6787101</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129367662</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>419339</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6787019</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129364490</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>419474</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6787027</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129357102</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>419519</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6787008</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129357108</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>419490</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6787103</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129357097</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>419496</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6786922</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129367665</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>419522</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6786991</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129364474</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79631</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>419457</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6787068</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129357128</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>419496</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6787068</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129357090</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>419367</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6786988</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129357093</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>419453</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6786995</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129367654</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>419298</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6787038</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129367670</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>419451</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6787144</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129367620</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>419497</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6787056</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129351462</v>
+        <v>129351476</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419354</v>
+        <v>419469</v>
       </c>
       <c r="R2" t="n">
-        <v>6787080</v>
+        <v>6787203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351476</v>
+        <v>129351462</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419469</v>
+        <v>419354</v>
       </c>
       <c r="R3" t="n">
-        <v>6787203</v>
+        <v>6787080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3136,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129357119</v>
+        <v>129357115</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419347</v>
+        <v>419460</v>
       </c>
       <c r="R25" t="n">
-        <v>6787070</v>
+        <v>6787130</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129357114</v>
+        <v>129367678</v>
       </c>
       <c r="B26" t="n">
         <v>79041</v>
@@ -3264,17 +3264,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419458</v>
+        <v>419262</v>
       </c>
       <c r="R26" t="n">
-        <v>6787193</v>
+        <v>6787031</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3318,19 +3318,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129357127</v>
+        <v>129357114</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419531</v>
+        <v>419458</v>
       </c>
       <c r="R27" t="n">
-        <v>6786974</v>
+        <v>6787193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,7 +3409,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3428,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357115</v>
+        <v>129357127</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3463,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419460</v>
+        <v>419531</v>
       </c>
       <c r="R28" t="n">
-        <v>6787130</v>
+        <v>6786974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,6 +3506,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3525,32 +3525,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129357038</v>
+        <v>129357119</v>
       </c>
       <c r="B29" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419467</v>
+        <v>419347</v>
       </c>
       <c r="R29" t="n">
-        <v>6787120</v>
+        <v>6787070</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,48 +3622,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129367678</v>
+        <v>129357038</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419262</v>
+        <v>419467</v>
       </c>
       <c r="R30" t="n">
-        <v>6787031</v>
+        <v>6787120</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3707,19 +3707,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357096</v>
+        <v>129357111</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419433</v>
+        <v>419456</v>
       </c>
       <c r="R31" t="n">
-        <v>6786954</v>
+        <v>6787149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357129</v>
+        <v>129357096</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419416</v>
+        <v>419433</v>
       </c>
       <c r="R33" t="n">
-        <v>6787118</v>
+        <v>6786954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3992,7 +3992,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4011,7 +4010,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129357111</v>
+        <v>129357129</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -4046,10 +4045,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419456</v>
+        <v>419416</v>
       </c>
       <c r="R34" t="n">
-        <v>6787149</v>
+        <v>6787118</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4090,6 +4089,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357106</v>
+        <v>129357105</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4243,7 +4243,7 @@
         <v>419505</v>
       </c>
       <c r="R36" t="n">
-        <v>6787037</v>
+        <v>6787028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357123</v>
+        <v>129357091</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419467</v>
+        <v>419411</v>
       </c>
       <c r="R38" t="n">
-        <v>6787011</v>
+        <v>6786979</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,7 +4479,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4498,7 +4497,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357105</v>
+        <v>129367674</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4529,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419505</v>
+        <v>419339</v>
       </c>
       <c r="R39" t="n">
-        <v>6787028</v>
+        <v>6787087</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4583,19 +4582,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357091</v>
+        <v>129357106</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4630,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419411</v>
+        <v>419505</v>
       </c>
       <c r="R40" t="n">
-        <v>6786979</v>
+        <v>6787037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129367674</v>
+        <v>129357123</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4723,17 +4722,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419339</v>
+        <v>419467</v>
       </c>
       <c r="R41" t="n">
-        <v>6787087</v>
+        <v>6787011</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4771,28 +4770,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129364483</v>
+        <v>129357095</v>
       </c>
       <c r="B42" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419459</v>
+        <v>419457</v>
       </c>
       <c r="R42" t="n">
-        <v>6786999</v>
+        <v>6786992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,12 +4874,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357095</v>
+        <v>129364483</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419457</v>
+        <v>419459</v>
       </c>
       <c r="R44" t="n">
-        <v>6786992</v>
+        <v>6786999</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,12 +5068,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367681</v>
+        <v>129364472</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419245</v>
+        <v>419439</v>
       </c>
       <c r="R48" t="n">
-        <v>6787037</v>
+        <v>6786970</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5456,19 +5456,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129367679</v>
+        <v>129364495</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5499,17 +5499,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419258</v>
+        <v>419475</v>
       </c>
       <c r="R49" t="n">
-        <v>6787042</v>
+        <v>6787178</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5553,19 +5553,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129364495</v>
+        <v>129364491</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419475</v>
+        <v>419450</v>
       </c>
       <c r="R50" t="n">
-        <v>6787178</v>
+        <v>6787079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129364491</v>
+        <v>129367679</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5693,17 +5693,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419450</v>
+        <v>419258</v>
       </c>
       <c r="R51" t="n">
-        <v>6787079</v>
+        <v>6787042</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5747,22 +5747,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364472</v>
+        <v>129367681</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,37 +5770,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419439</v>
+        <v>419245</v>
       </c>
       <c r="R52" t="n">
-        <v>6786970</v>
+        <v>6787037</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367619</v>
+        <v>129367607</v>
       </c>
       <c r="B54" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419457</v>
+        <v>419451</v>
       </c>
       <c r="R54" t="n">
-        <v>6787086</v>
+        <v>6787144</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,7 +6050,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367668</v>
+        <v>129367657</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419481</v>
+        <v>419454</v>
       </c>
       <c r="R55" t="n">
-        <v>6787056</v>
+        <v>6787097</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B56" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R56" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367657</v>
+        <v>129367619</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419454</v>
+        <v>419457</v>
       </c>
       <c r="R57" t="n">
-        <v>6787097</v>
+        <v>6787086</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129364497</v>
+        <v>129367666</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6372,17 +6372,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419476</v>
+        <v>419496</v>
       </c>
       <c r="R58" t="n">
-        <v>6787193</v>
+        <v>6787020</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6426,19 +6426,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129357103</v>
+        <v>129364497</v>
       </c>
       <c r="B59" t="n">
         <v>79041</v>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419509</v>
+        <v>419476</v>
       </c>
       <c r="R59" t="n">
-        <v>6787026</v>
+        <v>6787193</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6523,19 +6523,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357092</v>
+        <v>129357103</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419418</v>
+        <v>419509</v>
       </c>
       <c r="R60" t="n">
-        <v>6786979</v>
+        <v>6787026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129367666</v>
+        <v>129357092</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6663,17 +6663,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419496</v>
+        <v>419418</v>
       </c>
       <c r="R61" t="n">
-        <v>6787020</v>
+        <v>6786979</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6717,12 +6717,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129357121</v>
+        <v>129367663</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -6857,17 +6857,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419244</v>
+        <v>419353</v>
       </c>
       <c r="R63" t="n">
-        <v>6787051</v>
+        <v>6787020</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6911,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129367669</v>
+        <v>129357121</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7052,17 +7052,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419463</v>
+        <v>419244</v>
       </c>
       <c r="R65" t="n">
-        <v>6787067</v>
+        <v>6787051</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7106,19 +7106,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129367663</v>
+        <v>129367669</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419353</v>
+        <v>419463</v>
       </c>
       <c r="R66" t="n">
-        <v>6787020</v>
+        <v>6787067</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7215,7 +7215,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129367676</v>
+        <v>129367655</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419277</v>
+        <v>419317</v>
       </c>
       <c r="R67" t="n">
-        <v>6787033</v>
+        <v>6787029</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7312,7 +7312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367656</v>
+        <v>129367676</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419497</v>
+        <v>419277</v>
       </c>
       <c r="R68" t="n">
-        <v>6787027</v>
+        <v>6787033</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129367655</v>
+        <v>129357094</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419317</v>
+        <v>419463</v>
       </c>
       <c r="R69" t="n">
-        <v>6787029</v>
+        <v>6786985</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,19 +7494,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129367664</v>
+        <v>129367656</v>
       </c>
       <c r="B70" t="n">
         <v>79041</v>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419363</v>
+        <v>419497</v>
       </c>
       <c r="R70" t="n">
-        <v>6787023</v>
+        <v>6787027</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367651</v>
+        <v>129367653</v>
       </c>
       <c r="B71" t="n">
         <v>79041</v>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419250</v>
+        <v>419288</v>
       </c>
       <c r="R71" t="n">
-        <v>6787043</v>
+        <v>6787048</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7700,7 +7700,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367653</v>
+        <v>129364493</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7731,17 +7731,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419288</v>
+        <v>419438</v>
       </c>
       <c r="R72" t="n">
-        <v>6787048</v>
+        <v>6787138</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357094</v>
+        <v>129367664</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7828,17 +7828,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419463</v>
+        <v>419363</v>
       </c>
       <c r="R73" t="n">
-        <v>6786985</v>
+        <v>6787023</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7882,19 +7882,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129364493</v>
+        <v>129367651</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7925,17 +7925,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419438</v>
+        <v>419250</v>
       </c>
       <c r="R74" t="n">
-        <v>6787138</v>
+        <v>6787043</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7979,12 +7979,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129357117</v>
+        <v>129357118</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419364</v>
+        <v>419355</v>
       </c>
       <c r="R76" t="n">
         <v>6787091</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129357118</v>
+        <v>129357099</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419355</v>
+        <v>419529</v>
       </c>
       <c r="R77" t="n">
-        <v>6787091</v>
+        <v>6786987</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129357099</v>
+        <v>129357117</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419529</v>
+        <v>419364</v>
       </c>
       <c r="R78" t="n">
-        <v>6786987</v>
+        <v>6787091</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367658</v>
+        <v>129367677</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8414,10 +8414,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419264</v>
+        <v>419273</v>
       </c>
       <c r="R79" t="n">
-        <v>6787033</v>
+        <v>6787038</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129367677</v>
+        <v>129367658</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>419273</v>
+        <v>419264</v>
       </c>
       <c r="R80" t="n">
-        <v>6787038</v>
+        <v>6787033</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129367673</v>
+        <v>129364490</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -8604,17 +8604,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>419374</v>
+        <v>419474</v>
       </c>
       <c r="R81" t="n">
-        <v>6787101</v>
+        <v>6787027</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8658,12 +8658,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8767,7 +8767,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129364490</v>
+        <v>129367673</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -8798,17 +8798,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419474</v>
+        <v>419374</v>
       </c>
       <c r="R83" t="n">
-        <v>6787027</v>
+        <v>6787101</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8852,19 +8852,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357102</v>
+        <v>129357108</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419519</v>
+        <v>419490</v>
       </c>
       <c r="R84" t="n">
-        <v>6787008</v>
+        <v>6787103</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8961,7 +8961,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129357108</v>
+        <v>129357102</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419490</v>
+        <v>419519</v>
       </c>
       <c r="R85" t="n">
-        <v>6787103</v>
+        <v>6787008</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9349,7 +9349,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129357128</v>
+        <v>129367672</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -9380,17 +9380,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419496</v>
+        <v>419451</v>
       </c>
       <c r="R89" t="n">
-        <v>6787068</v>
+        <v>6787144</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9428,19 +9428,18 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9544,7 +9543,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357093</v>
+        <v>129357128</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9579,10 +9578,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419453</v>
+        <v>419496</v>
       </c>
       <c r="R91" t="n">
-        <v>6786995</v>
+        <v>6787068</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9623,6 +9622,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9641,7 +9641,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367654</v>
+        <v>129357093</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9672,17 +9672,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419298</v>
+        <v>419453</v>
       </c>
       <c r="R92" t="n">
-        <v>6787038</v>
+        <v>6786995</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9726,19 +9726,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129367670</v>
+        <v>129367654</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419451</v>
+        <v>419298</v>
       </c>
       <c r="R93" t="n">
-        <v>6787144</v>
+        <v>6787038</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129351476</v>
+        <v>129351462</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419469</v>
+        <v>419354</v>
       </c>
       <c r="R2" t="n">
-        <v>6787203</v>
+        <v>6787080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351462</v>
+        <v>129351476</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419354</v>
+        <v>419469</v>
       </c>
       <c r="R3" t="n">
-        <v>6787080</v>
+        <v>6787203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351438</v>
+        <v>129351460</v>
       </c>
       <c r="B21" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419388</v>
+        <v>419426</v>
       </c>
       <c r="R21" t="n">
-        <v>6787098</v>
+        <v>6787068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351460</v>
+        <v>129351438</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419426</v>
+        <v>419388</v>
       </c>
       <c r="R22" t="n">
-        <v>6787068</v>
+        <v>6787098</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357111</v>
+        <v>129357096</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419456</v>
+        <v>419433</v>
       </c>
       <c r="R31" t="n">
-        <v>6787149</v>
+        <v>6786954</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357110</v>
+        <v>129357111</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419465</v>
+        <v>419456</v>
       </c>
       <c r="R32" t="n">
-        <v>6787134</v>
+        <v>6787149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357096</v>
+        <v>129357110</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419433</v>
+        <v>419465</v>
       </c>
       <c r="R33" t="n">
-        <v>6786954</v>
+        <v>6787134</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357105</v>
+        <v>129367674</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419505</v>
+        <v>419339</v>
       </c>
       <c r="R36" t="n">
-        <v>6787028</v>
+        <v>6787087</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,19 +4290,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357125</v>
+        <v>129357106</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419485</v>
+        <v>419505</v>
       </c>
       <c r="R37" t="n">
-        <v>6786929</v>
+        <v>6787037</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,7 +4381,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4400,7 +4399,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357091</v>
+        <v>129357105</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4435,10 +4434,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419411</v>
+        <v>419505</v>
       </c>
       <c r="R38" t="n">
-        <v>6786979</v>
+        <v>6787028</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4497,7 +4496,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129367674</v>
+        <v>129357125</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4528,17 +4527,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419339</v>
+        <v>419485</v>
       </c>
       <c r="R39" t="n">
-        <v>6787087</v>
+        <v>6786929</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4576,25 +4575,26 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357106</v>
+        <v>129357091</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419505</v>
+        <v>419411</v>
       </c>
       <c r="R40" t="n">
-        <v>6787037</v>
+        <v>6786979</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129357095</v>
+        <v>129357109</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419457</v>
+        <v>419470</v>
       </c>
       <c r="R42" t="n">
-        <v>6786992</v>
+        <v>6787115</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357109</v>
+        <v>129357095</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419470</v>
+        <v>419457</v>
       </c>
       <c r="R43" t="n">
-        <v>6787115</v>
+        <v>6786992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357100</v>
+        <v>129357113</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419525</v>
+        <v>419460</v>
       </c>
       <c r="R46" t="n">
-        <v>6787008</v>
+        <v>6787178</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129357113</v>
+        <v>129357100</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419460</v>
+        <v>419525</v>
       </c>
       <c r="R47" t="n">
-        <v>6787178</v>
+        <v>6787008</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364472</v>
+        <v>129364495</v>
       </c>
       <c r="B48" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419439</v>
+        <v>419475</v>
       </c>
       <c r="R48" t="n">
-        <v>6786970</v>
+        <v>6787178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364495</v>
+        <v>129364491</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419475</v>
+        <v>419450</v>
       </c>
       <c r="R49" t="n">
-        <v>6787178</v>
+        <v>6787079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129364491</v>
+        <v>129367679</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5596,17 +5596,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419450</v>
+        <v>419258</v>
       </c>
       <c r="R50" t="n">
-        <v>6787079</v>
+        <v>6787042</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,19 +5650,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367679</v>
+        <v>129367681</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419258</v>
+        <v>419245</v>
       </c>
       <c r="R51" t="n">
-        <v>6787042</v>
+        <v>6787037</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367681</v>
+        <v>129364472</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,37 +5770,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419245</v>
+        <v>419439</v>
       </c>
       <c r="R52" t="n">
-        <v>6787037</v>
+        <v>6786970</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B54" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R54" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367668</v>
+        <v>129367619</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419481</v>
+        <v>419457</v>
       </c>
       <c r="R56" t="n">
-        <v>6787056</v>
+        <v>6787086</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367619</v>
+        <v>129367607</v>
       </c>
       <c r="B57" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419457</v>
+        <v>419451</v>
       </c>
       <c r="R57" t="n">
-        <v>6787086</v>
+        <v>6787144</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357092</v>
+        <v>129367680</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6663,17 +6663,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419418</v>
+        <v>419248</v>
       </c>
       <c r="R61" t="n">
-        <v>6786979</v>
+        <v>6787041</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6717,19 +6717,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129367680</v>
+        <v>129357092</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6760,17 +6760,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419248</v>
+        <v>419418</v>
       </c>
       <c r="R62" t="n">
-        <v>6787041</v>
+        <v>6786979</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6814,19 +6814,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367663</v>
+        <v>129367669</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419353</v>
+        <v>419463</v>
       </c>
       <c r="R63" t="n">
-        <v>6787020</v>
+        <v>6787067</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357126</v>
+        <v>129367663</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -6954,17 +6954,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419522</v>
+        <v>419353</v>
       </c>
       <c r="R64" t="n">
-        <v>6786923</v>
+        <v>6787020</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7002,26 +7002,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357121</v>
+        <v>129357126</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7056,10 +7055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419244</v>
+        <v>419522</v>
       </c>
       <c r="R65" t="n">
-        <v>6787051</v>
+        <v>6786923</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7100,6 +7099,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7118,7 +7118,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129367669</v>
+        <v>129357121</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7149,17 +7149,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419463</v>
+        <v>419244</v>
       </c>
       <c r="R66" t="n">
-        <v>6787067</v>
+        <v>6787051</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7203,19 +7203,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129367655</v>
+        <v>129357094</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7246,17 +7246,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419317</v>
+        <v>419463</v>
       </c>
       <c r="R67" t="n">
-        <v>6787029</v>
+        <v>6786985</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7300,19 +7300,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367676</v>
+        <v>129367655</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419277</v>
+        <v>419317</v>
       </c>
       <c r="R68" t="n">
-        <v>6787033</v>
+        <v>6787029</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357094</v>
+        <v>129367676</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419463</v>
+        <v>419277</v>
       </c>
       <c r="R69" t="n">
-        <v>6786985</v>
+        <v>6787033</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,12 +7494,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129357118</v>
+        <v>129357117</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419355</v>
+        <v>419364</v>
       </c>
       <c r="R76" t="n">
         <v>6787091</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129357099</v>
+        <v>129367658</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8216,17 +8216,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419529</v>
+        <v>419264</v>
       </c>
       <c r="R77" t="n">
-        <v>6786987</v>
+        <v>6787033</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8270,19 +8270,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129357117</v>
+        <v>129357118</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419364</v>
+        <v>419355</v>
       </c>
       <c r="R78" t="n">
         <v>6787091</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129367677</v>
+        <v>129357099</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8410,17 +8410,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419273</v>
+        <v>419529</v>
       </c>
       <c r="R79" t="n">
-        <v>6787038</v>
+        <v>6786987</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8464,19 +8464,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129367658</v>
+        <v>129367677</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>419264</v>
+        <v>419273</v>
       </c>
       <c r="R80" t="n">
-        <v>6787033</v>
+        <v>6787038</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9058,7 +9058,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357097</v>
+        <v>129367665</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9089,17 +9089,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419496</v>
+        <v>419522</v>
       </c>
       <c r="R86" t="n">
-        <v>6786922</v>
+        <v>6786991</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9143,19 +9143,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367665</v>
+        <v>129357097</v>
       </c>
       <c r="B87" t="n">
         <v>79041</v>
@@ -9186,17 +9186,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419522</v>
+        <v>419496</v>
       </c>
       <c r="R87" t="n">
-        <v>6786991</v>
+        <v>6786922</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9240,12 +9240,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357090</v>
+        <v>129367654</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9477,17 +9477,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419367</v>
+        <v>419298</v>
       </c>
       <c r="R90" t="n">
-        <v>6786988</v>
+        <v>6787038</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9531,19 +9531,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357128</v>
+        <v>129357090</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9578,10 +9578,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419496</v>
+        <v>419367</v>
       </c>
       <c r="R91" t="n">
-        <v>6787068</v>
+        <v>6786988</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9622,7 +9622,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9641,7 +9640,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357093</v>
+        <v>129357128</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9676,10 +9675,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419453</v>
+        <v>419496</v>
       </c>
       <c r="R92" t="n">
-        <v>6786995</v>
+        <v>6787068</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9720,6 +9719,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9738,7 +9738,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129367654</v>
+        <v>129357093</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9769,17 +9769,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419298</v>
+        <v>419453</v>
       </c>
       <c r="R93" t="n">
-        <v>6787038</v>
+        <v>6786995</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9823,12 +9823,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129357115</v>
+        <v>129357038</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419460</v>
+        <v>419467</v>
       </c>
       <c r="R25" t="n">
-        <v>6787130</v>
+        <v>6787120</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129357114</v>
+        <v>129357115</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419458</v>
+        <v>419460</v>
       </c>
       <c r="R27" t="n">
-        <v>6787193</v>
+        <v>6787130</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357127</v>
+        <v>129357114</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419531</v>
+        <v>419458</v>
       </c>
       <c r="R28" t="n">
-        <v>6786974</v>
+        <v>6787193</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,7 +3506,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3525,7 +3524,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129357119</v>
+        <v>129357127</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3560,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419347</v>
+        <v>419531</v>
       </c>
       <c r="R29" t="n">
-        <v>6787070</v>
+        <v>6786974</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,6 +3603,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3622,32 +3622,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129357038</v>
+        <v>129357119</v>
       </c>
       <c r="B30" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419467</v>
+        <v>419347</v>
       </c>
       <c r="R30" t="n">
-        <v>6787120</v>
+        <v>6787070</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357096</v>
+        <v>129357111</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419433</v>
+        <v>419456</v>
       </c>
       <c r="R31" t="n">
-        <v>6786954</v>
+        <v>6787149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357111</v>
+        <v>129357110</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419456</v>
+        <v>419465</v>
       </c>
       <c r="R32" t="n">
-        <v>6787149</v>
+        <v>6787134</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357110</v>
+        <v>129357096</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419465</v>
+        <v>419433</v>
       </c>
       <c r="R33" t="n">
-        <v>6787134</v>
+        <v>6786954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129367674</v>
+        <v>129357105</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419339</v>
+        <v>419505</v>
       </c>
       <c r="R36" t="n">
-        <v>6787087</v>
+        <v>6787028</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,19 +4290,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357106</v>
+        <v>129357125</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419505</v>
+        <v>419485</v>
       </c>
       <c r="R37" t="n">
-        <v>6787037</v>
+        <v>6786929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,6 +4381,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,7 +4400,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357105</v>
+        <v>129357091</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4434,10 +4435,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419505</v>
+        <v>419411</v>
       </c>
       <c r="R38" t="n">
-        <v>6787028</v>
+        <v>6786979</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4496,7 +4497,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357125</v>
+        <v>129367674</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4527,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419485</v>
+        <v>419339</v>
       </c>
       <c r="R39" t="n">
-        <v>6786929</v>
+        <v>6787087</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4575,26 +4576,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357091</v>
+        <v>129357106</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419411</v>
+        <v>419505</v>
       </c>
       <c r="R40" t="n">
-        <v>6786979</v>
+        <v>6787037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129357109</v>
+        <v>129357095</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419470</v>
+        <v>419457</v>
       </c>
       <c r="R42" t="n">
-        <v>6787115</v>
+        <v>6786992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357095</v>
+        <v>129357109</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419457</v>
+        <v>419470</v>
       </c>
       <c r="R43" t="n">
-        <v>6786992</v>
+        <v>6787115</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357113</v>
+        <v>129357100</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419460</v>
+        <v>419525</v>
       </c>
       <c r="R46" t="n">
-        <v>6787178</v>
+        <v>6787008</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129357100</v>
+        <v>129357113</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419525</v>
+        <v>419460</v>
       </c>
       <c r="R47" t="n">
-        <v>6787008</v>
+        <v>6787178</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364495</v>
+        <v>129367681</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5402,17 +5402,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419475</v>
+        <v>419245</v>
       </c>
       <c r="R48" t="n">
-        <v>6787178</v>
+        <v>6787037</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5456,19 +5456,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364491</v>
+        <v>129367679</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5499,17 +5499,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419450</v>
+        <v>419258</v>
       </c>
       <c r="R49" t="n">
-        <v>6787079</v>
+        <v>6787042</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5553,22 +5553,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367679</v>
+        <v>129364472</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5576,37 +5576,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419258</v>
+        <v>419439</v>
       </c>
       <c r="R50" t="n">
-        <v>6787042</v>
+        <v>6786970</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,19 +5650,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367681</v>
+        <v>129364495</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5693,17 +5693,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419245</v>
+        <v>419475</v>
       </c>
       <c r="R51" t="n">
-        <v>6787037</v>
+        <v>6787178</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5747,22 +5747,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364472</v>
+        <v>129364491</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,21 +5770,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419439</v>
+        <v>419450</v>
       </c>
       <c r="R52" t="n">
-        <v>6786970</v>
+        <v>6787079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367668</v>
+        <v>129367657</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419481</v>
+        <v>419454</v>
       </c>
       <c r="R54" t="n">
-        <v>6787056</v>
+        <v>6787097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,7 +6050,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367657</v>
+        <v>129367668</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419454</v>
+        <v>419481</v>
       </c>
       <c r="R55" t="n">
-        <v>6787097</v>
+        <v>6787056</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129367680</v>
+        <v>129357092</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6663,17 +6663,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419248</v>
+        <v>419418</v>
       </c>
       <c r="R61" t="n">
-        <v>6787041</v>
+        <v>6786979</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6717,19 +6717,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357092</v>
+        <v>129367680</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6760,17 +6760,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419418</v>
+        <v>419248</v>
       </c>
       <c r="R62" t="n">
-        <v>6786979</v>
+        <v>6787041</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6814,12 +6814,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7312,7 +7312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367655</v>
+        <v>129367653</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419317</v>
+        <v>419288</v>
       </c>
       <c r="R68" t="n">
-        <v>6787029</v>
+        <v>6787048</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129367676</v>
+        <v>129364493</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419277</v>
+        <v>419438</v>
       </c>
       <c r="R69" t="n">
-        <v>6787033</v>
+        <v>6787138</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,19 +7494,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129367656</v>
+        <v>129367664</v>
       </c>
       <c r="B70" t="n">
         <v>79041</v>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419497</v>
+        <v>419363</v>
       </c>
       <c r="R70" t="n">
-        <v>6787027</v>
+        <v>6787023</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367653</v>
+        <v>129367655</v>
       </c>
       <c r="B71" t="n">
         <v>79041</v>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419288</v>
+        <v>419317</v>
       </c>
       <c r="R71" t="n">
-        <v>6787048</v>
+        <v>6787029</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7700,7 +7700,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129364493</v>
+        <v>129367676</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7731,17 +7731,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419438</v>
+        <v>419277</v>
       </c>
       <c r="R72" t="n">
-        <v>6787138</v>
+        <v>6787033</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367664</v>
+        <v>129367656</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419363</v>
+        <v>419497</v>
       </c>
       <c r="R73" t="n">
-        <v>6787023</v>
+        <v>6787027</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129357117</v>
+        <v>129357118</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419364</v>
+        <v>419355</v>
       </c>
       <c r="R76" t="n">
         <v>6787091</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129367658</v>
+        <v>129357099</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8216,17 +8216,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419264</v>
+        <v>419529</v>
       </c>
       <c r="R77" t="n">
-        <v>6787033</v>
+        <v>6786987</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8270,19 +8270,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129357118</v>
+        <v>129357117</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419355</v>
+        <v>419364</v>
       </c>
       <c r="R78" t="n">
         <v>6787091</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129357099</v>
+        <v>129367677</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8410,17 +8410,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>419529</v>
+        <v>419273</v>
       </c>
       <c r="R79" t="n">
-        <v>6786987</v>
+        <v>6787038</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8464,19 +8464,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129367677</v>
+        <v>129367658</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>419273</v>
+        <v>419264</v>
       </c>
       <c r="R80" t="n">
-        <v>6787038</v>
+        <v>6787033</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129367665</v>
+        <v>129364474</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9069,37 +9069,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419522</v>
+        <v>419457</v>
       </c>
       <c r="R86" t="n">
-        <v>6786991</v>
+        <v>6787068</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9143,12 +9143,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9252,10 +9252,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129364474</v>
+        <v>129367665</v>
       </c>
       <c r="B88" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9263,37 +9263,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419457</v>
+        <v>419522</v>
       </c>
       <c r="R88" t="n">
-        <v>6787068</v>
+        <v>6786991</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9337,19 +9337,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367672</v>
+        <v>129367670</v>
       </c>
       <c r="B89" t="n">
         <v>79041</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367654</v>
+        <v>129357093</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9477,17 +9477,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419298</v>
+        <v>419453</v>
       </c>
       <c r="R90" t="n">
-        <v>6787038</v>
+        <v>6786995</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9531,19 +9531,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357090</v>
+        <v>129367654</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9574,17 +9574,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419367</v>
+        <v>419298</v>
       </c>
       <c r="R91" t="n">
-        <v>6786988</v>
+        <v>6787038</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9628,19 +9628,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357128</v>
+        <v>129357090</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419496</v>
+        <v>419367</v>
       </c>
       <c r="R92" t="n">
-        <v>6787068</v>
+        <v>6786988</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9719,7 +9719,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9738,7 +9737,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129357093</v>
+        <v>129357128</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9773,10 +9772,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419453</v>
+        <v>419496</v>
       </c>
       <c r="R93" t="n">
-        <v>6786995</v>
+        <v>6787068</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9817,6 +9816,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351462</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351476</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351439</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351440</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351455</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351471</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351464</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351475</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351461</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351458</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351459</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351469</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351472</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129351467</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351474</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351473</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351466</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351457</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351465</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>129351460</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>129351438</v>
       </c>
       <c r="B22" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129351470</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351468</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129367678</v>
+        <v>129357115</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,17 +3264,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419262</v>
+        <v>419460</v>
       </c>
       <c r="R26" t="n">
-        <v>6787031</v>
+        <v>6787130</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3318,22 +3318,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129357115</v>
+        <v>129367678</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,17 +3361,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419460</v>
+        <v>419262</v>
       </c>
       <c r="R27" t="n">
-        <v>6787130</v>
+        <v>6787031</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3415,12 +3415,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
         <v>129357114</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>129357127</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>129357119</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129357111</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>129357110</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>129357096</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129357129</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>129357107</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>129357105</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>129357125</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>129357091</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129367674</v>
+        <v>129357106</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419339</v>
+        <v>419505</v>
       </c>
       <c r="R39" t="n">
-        <v>6787087</v>
+        <v>6787037</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,22 +4582,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357106</v>
+        <v>129357123</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419505</v>
+        <v>419467</v>
       </c>
       <c r="R40" t="n">
-        <v>6787037</v>
+        <v>6787011</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,6 +4673,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357123</v>
+        <v>129367674</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4722,17 +4723,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419467</v>
+        <v>419339</v>
       </c>
       <c r="R41" t="n">
-        <v>6787011</v>
+        <v>6787087</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4770,29 +4771,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129357095</v>
+        <v>129357109</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419457</v>
+        <v>419470</v>
       </c>
       <c r="R42" t="n">
-        <v>6786992</v>
+        <v>6787115</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4886,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357109</v>
+        <v>129364483</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419470</v>
+        <v>419459</v>
       </c>
       <c r="R43" t="n">
-        <v>6787115</v>
+        <v>6786999</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,22 +4971,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129364483</v>
+        <v>129357095</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419459</v>
+        <v>419457</v>
       </c>
       <c r="R44" t="n">
-        <v>6786999</v>
+        <v>6786992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,22 +5068,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367675</v>
+        <v>129357100</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5111,17 +5111,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419314</v>
+        <v>419525</v>
       </c>
       <c r="R45" t="n">
-        <v>6787092</v>
+        <v>6787008</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,22 +5165,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357100</v>
+        <v>129357113</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419525</v>
+        <v>419460</v>
       </c>
       <c r="R46" t="n">
-        <v>6787008</v>
+        <v>6787178</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129357113</v>
+        <v>129367675</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,17 +5305,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419460</v>
+        <v>419314</v>
       </c>
       <c r="R47" t="n">
-        <v>6787178</v>
+        <v>6787092</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,22 +5359,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367681</v>
+        <v>129364491</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,17 +5402,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419245</v>
+        <v>419450</v>
       </c>
       <c r="R48" t="n">
-        <v>6787037</v>
+        <v>6787079</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5456,22 +5456,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129367679</v>
+        <v>129364495</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5499,17 +5499,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419258</v>
+        <v>419475</v>
       </c>
       <c r="R49" t="n">
-        <v>6787042</v>
+        <v>6787178</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5553,22 +5553,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129364472</v>
+        <v>129367679</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5576,37 +5576,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419439</v>
+        <v>419258</v>
       </c>
       <c r="R50" t="n">
-        <v>6786970</v>
+        <v>6787042</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129364495</v>
+        <v>129364472</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419475</v>
+        <v>419439</v>
       </c>
       <c r="R51" t="n">
-        <v>6787178</v>
+        <v>6786970</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364491</v>
+        <v>129367681</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5790,17 +5790,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419450</v>
+        <v>419245</v>
       </c>
       <c r="R52" t="n">
-        <v>6787079</v>
+        <v>6787037</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
         <v>129367652</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>129367657</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>129367668</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>129367619</v>
       </c>
       <c r="B56" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>129367607</v>
       </c>
       <c r="B57" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>129367666</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129364497</v>
+        <v>129357103</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419476</v>
+        <v>419509</v>
       </c>
       <c r="R59" t="n">
-        <v>6787193</v>
+        <v>6787026</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6523,22 +6523,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357103</v>
+        <v>129357092</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419509</v>
+        <v>419418</v>
       </c>
       <c r="R60" t="n">
-        <v>6787026</v>
+        <v>6786979</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357092</v>
+        <v>129367680</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6663,17 +6663,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419418</v>
+        <v>419248</v>
       </c>
       <c r="R61" t="n">
-        <v>6786979</v>
+        <v>6787041</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6717,22 +6717,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129367680</v>
+        <v>129364497</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6760,17 +6760,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419248</v>
+        <v>419476</v>
       </c>
       <c r="R62" t="n">
-        <v>6787041</v>
+        <v>6787193</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6814,22 +6814,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367669</v>
+        <v>129357126</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,17 +6857,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419463</v>
+        <v>419522</v>
       </c>
       <c r="R63" t="n">
-        <v>6787067</v>
+        <v>6786923</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6905,28 +6905,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129367663</v>
+        <v>129357121</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6954,17 +6955,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419353</v>
+        <v>419244</v>
       </c>
       <c r="R64" t="n">
-        <v>6787020</v>
+        <v>6787051</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7008,22 +7009,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357126</v>
+        <v>129367669</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7051,17 +7052,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419522</v>
+        <v>419463</v>
       </c>
       <c r="R65" t="n">
-        <v>6786923</v>
+        <v>6787067</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7099,29 +7100,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357121</v>
+        <v>129367663</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7149,17 +7149,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419244</v>
+        <v>419353</v>
       </c>
       <c r="R66" t="n">
-        <v>6787051</v>
+        <v>6787020</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7203,12 +7203,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
         <v>129357094</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7312,10 +7312,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367653</v>
+        <v>129367656</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419288</v>
+        <v>419497</v>
       </c>
       <c r="R68" t="n">
-        <v>6787048</v>
+        <v>6787027</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129364493</v>
+        <v>129367653</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419438</v>
+        <v>419288</v>
       </c>
       <c r="R69" t="n">
-        <v>6787138</v>
+        <v>6787048</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,12 +7494,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7509,7 +7509,7 @@
         <v>129367664</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367655</v>
+        <v>129367651</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419317</v>
+        <v>419250</v>
       </c>
       <c r="R71" t="n">
-        <v>6787029</v>
+        <v>6787043</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367676</v>
+        <v>129367655</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419277</v>
+        <v>419317</v>
       </c>
       <c r="R72" t="n">
-        <v>6787033</v>
+        <v>6787029</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7797,10 +7797,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367656</v>
+        <v>129367676</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419497</v>
+        <v>419277</v>
       </c>
       <c r="R73" t="n">
-        <v>6787027</v>
+        <v>6787033</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7894,10 +7894,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367651</v>
+        <v>129364493</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7925,17 +7925,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419250</v>
+        <v>419438</v>
       </c>
       <c r="R74" t="n">
-        <v>6787043</v>
+        <v>6787138</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7979,12 +7979,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7994,7 +7994,7 @@
         <v>129357120</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>129357118</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>129357099</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>129357117</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>129367677</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>129367658</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129364490</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8670,10 +8670,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129367662</v>
+        <v>129367673</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>419339</v>
+        <v>419374</v>
       </c>
       <c r="R82" t="n">
-        <v>6787019</v>
+        <v>6787101</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8767,10 +8767,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129367673</v>
+        <v>129367662</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>419374</v>
+        <v>419339</v>
       </c>
       <c r="R83" t="n">
-        <v>6787101</v>
+        <v>6787019</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8867,7 +8867,7 @@
         <v>129357108</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>129357102</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129364474</v>
+        <v>129357097</v>
       </c>
       <c r="B86" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9069,21 +9069,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419457</v>
+        <v>419496</v>
       </c>
       <c r="R86" t="n">
-        <v>6787068</v>
+        <v>6786922</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9143,22 +9143,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357097</v>
+        <v>129367665</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9186,17 +9186,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419496</v>
+        <v>419522</v>
       </c>
       <c r="R87" t="n">
-        <v>6786922</v>
+        <v>6786991</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9240,22 +9240,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367665</v>
+        <v>129364474</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9263,37 +9263,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419522</v>
+        <v>419457</v>
       </c>
       <c r="R88" t="n">
-        <v>6786991</v>
+        <v>6787068</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9337,22 +9337,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129367670</v>
+        <v>129367672</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9446,10 +9446,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357093</v>
+        <v>129357128</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419453</v>
+        <v>419496</v>
       </c>
       <c r="R90" t="n">
-        <v>6786995</v>
+        <v>6787068</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9525,6 +9525,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9546,7 +9547,7 @@
         <v>129367654</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9643,7 +9644,7 @@
         <v>129357090</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9737,10 +9738,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129357128</v>
+        <v>129357093</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9772,10 +9773,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>419496</v>
+        <v>419453</v>
       </c>
       <c r="R93" t="n">
-        <v>6787068</v>
+        <v>6786995</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9816,7 +9817,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351462</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351476</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351439</v>
       </c>
       <c r="B4" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351440</v>
       </c>
       <c r="B5" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351455</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351471</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351464</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351461</v>
+        <v>129351475</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>419368</v>
+        <v>419460</v>
       </c>
       <c r="R9" t="n">
-        <v>6787075</v>
+        <v>6787207</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351475</v>
+        <v>129351461</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>419460</v>
+        <v>419368</v>
       </c>
       <c r="R10" t="n">
-        <v>6787207</v>
+        <v>6787075</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351459</v>
+        <v>129351458</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>419435</v>
+        <v>419468</v>
       </c>
       <c r="R11" t="n">
-        <v>6787056</v>
+        <v>6787026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351458</v>
+        <v>129351459</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>419468</v>
+        <v>419435</v>
       </c>
       <c r="R12" t="n">
-        <v>6787026</v>
+        <v>6787056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>129351469</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351472</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129351467</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351474</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351473</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351466</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351457</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129351465</v>
+        <v>129351438</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419384</v>
+        <v>419388</v>
       </c>
       <c r="R20" t="n">
-        <v>6787088</v>
+        <v>6787098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351460</v>
+        <v>129351465</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419426</v>
+        <v>419384</v>
       </c>
       <c r="R21" t="n">
-        <v>6787068</v>
+        <v>6787088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351438</v>
+        <v>129351460</v>
       </c>
       <c r="B22" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419388</v>
+        <v>419426</v>
       </c>
       <c r="R22" t="n">
-        <v>6787098</v>
+        <v>6787068</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351468</v>
+        <v>129351470</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>419465</v>
+        <v>419470</v>
       </c>
       <c r="R23" t="n">
-        <v>6787144</v>
+        <v>6787160</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351470</v>
+        <v>129351468</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>419470</v>
+        <v>419465</v>
       </c>
       <c r="R24" t="n">
-        <v>6787160</v>
+        <v>6787144</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129357127</v>
+        <v>129357115</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>419531</v>
+        <v>419460</v>
       </c>
       <c r="R25" t="n">
-        <v>6786974</v>
+        <v>6787130</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3215,7 +3215,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3234,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129357114</v>
+        <v>129367678</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,17 +3264,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>419458</v>
+        <v>419262</v>
       </c>
       <c r="R26" t="n">
-        <v>6787193</v>
+        <v>6787031</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3319,22 +3318,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129357115</v>
+        <v>129357114</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3366,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419460</v>
+        <v>419458</v>
       </c>
       <c r="R27" t="n">
-        <v>6787130</v>
+        <v>6787193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3428,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357119</v>
+        <v>129357127</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3463,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419347</v>
+        <v>419531</v>
       </c>
       <c r="R28" t="n">
-        <v>6787070</v>
+        <v>6786974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,6 +3506,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3525,32 +3525,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129357038</v>
+        <v>129357119</v>
       </c>
       <c r="B29" t="n">
-        <v>56920</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>419467</v>
+        <v>419347</v>
       </c>
       <c r="R29" t="n">
-        <v>6787120</v>
+        <v>6787070</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,48 +3622,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129367678</v>
+        <v>129357038</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>56925</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>419262</v>
+        <v>419467</v>
       </c>
       <c r="R30" t="n">
-        <v>6787031</v>
+        <v>6787120</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3707,22 +3707,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357129</v>
+        <v>129357110</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419416</v>
+        <v>419465</v>
       </c>
       <c r="R31" t="n">
-        <v>6787118</v>
+        <v>6787134</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3798,7 +3798,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3817,10 +3816,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357096</v>
+        <v>129357129</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,10 +3851,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419433</v>
+        <v>419416</v>
       </c>
       <c r="R32" t="n">
-        <v>6786954</v>
+        <v>6787118</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3896,6 +3895,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3914,10 +3914,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357110</v>
+        <v>129357111</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419465</v>
+        <v>419456</v>
       </c>
       <c r="R33" t="n">
-        <v>6787134</v>
+        <v>6787149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129357111</v>
+        <v>129357096</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419456</v>
+        <v>419433</v>
       </c>
       <c r="R34" t="n">
-        <v>6787149</v>
+        <v>6786954</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4111,7 +4111,7 @@
         <v>129357107</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357106</v>
+        <v>129357105</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>419505</v>
       </c>
       <c r="R36" t="n">
-        <v>6787037</v>
+        <v>6787028</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4302,10 +4302,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357123</v>
+        <v>129357125</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419467</v>
+        <v>419485</v>
       </c>
       <c r="R37" t="n">
-        <v>6787011</v>
+        <v>6786929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357105</v>
+        <v>129357091</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419505</v>
+        <v>419411</v>
       </c>
       <c r="R38" t="n">
-        <v>6787028</v>
+        <v>6786979</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357091</v>
+        <v>129367674</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419411</v>
+        <v>419339</v>
       </c>
       <c r="R39" t="n">
-        <v>6786979</v>
+        <v>6787087</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,22 +4582,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357125</v>
+        <v>129357106</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419485</v>
+        <v>419505</v>
       </c>
       <c r="R40" t="n">
-        <v>6786929</v>
+        <v>6787037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,7 +4673,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4692,10 +4691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129367674</v>
+        <v>129357123</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4723,17 +4722,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419339</v>
+        <v>419467</v>
       </c>
       <c r="R41" t="n">
-        <v>6787087</v>
+        <v>6787011</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4771,28 +4770,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129364483</v>
+        <v>129357095</v>
       </c>
       <c r="B42" t="n">
-        <v>78827</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419459</v>
+        <v>419457</v>
       </c>
       <c r="R42" t="n">
-        <v>6786999</v>
+        <v>6786992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,22 +4874,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357095</v>
+        <v>129357109</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419457</v>
+        <v>419470</v>
       </c>
       <c r="R43" t="n">
-        <v>6786992</v>
+        <v>6787115</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357109</v>
+        <v>129364483</v>
       </c>
       <c r="B44" t="n">
-        <v>79070</v>
+        <v>78832</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419470</v>
+        <v>419459</v>
       </c>
       <c r="R44" t="n">
-        <v>6787115</v>
+        <v>6786999</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,22 +5068,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357113</v>
+        <v>129367675</v>
       </c>
       <c r="B45" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5111,17 +5111,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419460</v>
+        <v>419314</v>
       </c>
       <c r="R45" t="n">
-        <v>6787178</v>
+        <v>6787092</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,12 +5165,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5180,7 +5180,7 @@
         <v>129357100</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129367675</v>
+        <v>129357113</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,17 +5305,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>419314</v>
+        <v>419460</v>
       </c>
       <c r="R47" t="n">
-        <v>6787092</v>
+        <v>6787178</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5359,22 +5359,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364491</v>
+        <v>129364495</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419450</v>
+        <v>419475</v>
       </c>
       <c r="R48" t="n">
-        <v>6787079</v>
+        <v>6787178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5468,10 +5468,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364495</v>
+        <v>129364491</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419475</v>
+        <v>419450</v>
       </c>
       <c r="R49" t="n">
-        <v>6787178</v>
+        <v>6787079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
         <v>129367679</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>129367681</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>129364472</v>
       </c>
       <c r="B52" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>129367652</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>129367619</v>
       </c>
       <c r="B54" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>129367607</v>
       </c>
       <c r="B55" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367668</v>
+        <v>129367657</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419481</v>
+        <v>419454</v>
       </c>
       <c r="R56" t="n">
-        <v>6787056</v>
+        <v>6787097</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367657</v>
+        <v>129367668</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419454</v>
+        <v>419481</v>
       </c>
       <c r="R57" t="n">
-        <v>6787097</v>
+        <v>6787056</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129357103</v>
+        <v>129367666</v>
       </c>
       <c r="B58" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6372,17 +6372,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419509</v>
+        <v>419496</v>
       </c>
       <c r="R58" t="n">
-        <v>6787026</v>
+        <v>6787020</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6426,12 +6426,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6441,7 +6441,7 @@
         <v>129364497</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357092</v>
+        <v>129357103</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419418</v>
+        <v>419509</v>
       </c>
       <c r="R60" t="n">
-        <v>6786979</v>
+        <v>6787026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129367666</v>
+        <v>129357092</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6663,17 +6663,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419496</v>
+        <v>419418</v>
       </c>
       <c r="R61" t="n">
-        <v>6787020</v>
+        <v>6786979</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6717,12 +6717,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6732,7 +6732,7 @@
         <v>129367680</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367663</v>
+        <v>129367669</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419353</v>
+        <v>419463</v>
       </c>
       <c r="R63" t="n">
-        <v>6787020</v>
+        <v>6787067</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357121</v>
+        <v>129367663</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6954,17 +6954,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419244</v>
+        <v>419353</v>
       </c>
       <c r="R64" t="n">
-        <v>6787051</v>
+        <v>6787020</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357126</v>
+        <v>129357121</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419522</v>
+        <v>419244</v>
       </c>
       <c r="R65" t="n">
-        <v>6786923</v>
+        <v>6787051</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7099,7 +7099,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7118,10 +7117,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129367669</v>
+        <v>129357126</v>
       </c>
       <c r="B66" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7149,17 +7148,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419463</v>
+        <v>419522</v>
       </c>
       <c r="R66" t="n">
-        <v>6787067</v>
+        <v>6786923</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7197,28 +7196,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129364493</v>
+        <v>129367655</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7246,17 +7246,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419438</v>
+        <v>419317</v>
       </c>
       <c r="R67" t="n">
-        <v>6787138</v>
+        <v>6787029</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7300,22 +7300,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367664</v>
+        <v>129367676</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419363</v>
+        <v>419277</v>
       </c>
       <c r="R68" t="n">
-        <v>6787023</v>
+        <v>6787033</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129367653</v>
+        <v>129367656</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419288</v>
+        <v>419497</v>
       </c>
       <c r="R69" t="n">
-        <v>6787048</v>
+        <v>6787027</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7506,10 +7506,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129357094</v>
+        <v>129367653</v>
       </c>
       <c r="B70" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7537,17 +7537,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419463</v>
+        <v>419288</v>
       </c>
       <c r="R70" t="n">
-        <v>6786985</v>
+        <v>6787048</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7591,22 +7591,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367655</v>
+        <v>129364493</v>
       </c>
       <c r="B71" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7634,17 +7634,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419317</v>
+        <v>419438</v>
       </c>
       <c r="R71" t="n">
-        <v>6787029</v>
+        <v>6787138</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7688,22 +7688,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367676</v>
+        <v>129367664</v>
       </c>
       <c r="B72" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419277</v>
+        <v>419363</v>
       </c>
       <c r="R72" t="n">
-        <v>6787033</v>
+        <v>6787023</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7797,10 +7797,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367656</v>
+        <v>129357094</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7828,17 +7828,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419497</v>
+        <v>419463</v>
       </c>
       <c r="R73" t="n">
-        <v>6787027</v>
+        <v>6786985</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7882,12 +7882,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7897,7 +7897,7 @@
         <v>129367651</v>
       </c>
       <c r="B74" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>129357120</v>
       </c>
       <c r="B75" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8088,10 +8088,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129357117</v>
+        <v>129357118</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>419364</v>
+        <v>419355</v>
       </c>
       <c r="R76" t="n">
         <v>6787091</v>
@@ -8185,10 +8185,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129357118</v>
+        <v>129357099</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>419355</v>
+        <v>419529</v>
       </c>
       <c r="R77" t="n">
-        <v>6787091</v>
+        <v>6786987</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8282,10 +8282,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129357099</v>
+        <v>129357117</v>
       </c>
       <c r="B78" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>419529</v>
+        <v>419364</v>
       </c>
       <c r="R78" t="n">
-        <v>6786987</v>
+        <v>6787091</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8382,7 +8382,7 @@
         <v>129367677</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>129367658</v>
       </c>
       <c r="B80" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8573,10 +8573,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129367662</v>
+        <v>129364490</v>
       </c>
       <c r="B81" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8604,17 +8604,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>419339</v>
+        <v>419474</v>
       </c>
       <c r="R81" t="n">
-        <v>6787019</v>
+        <v>6787027</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8658,22 +8658,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129364490</v>
+        <v>129367662</v>
       </c>
       <c r="B82" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8701,17 +8701,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>419474</v>
+        <v>419339</v>
       </c>
       <c r="R82" t="n">
-        <v>6787027</v>
+        <v>6787019</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8755,12 +8755,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8770,7 +8770,7 @@
         <v>129367673</v>
       </c>
       <c r="B83" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8864,10 +8864,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129357102</v>
+        <v>129357108</v>
       </c>
       <c r="B84" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>419519</v>
+        <v>419490</v>
       </c>
       <c r="R84" t="n">
-        <v>6787008</v>
+        <v>6787103</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8961,10 +8961,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129357108</v>
+        <v>129357102</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>419490</v>
+        <v>419519</v>
       </c>
       <c r="R85" t="n">
-        <v>6787103</v>
+        <v>6787008</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357097</v>
+        <v>129367665</v>
       </c>
       <c r="B86" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9089,17 +9089,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419496</v>
+        <v>419522</v>
       </c>
       <c r="R86" t="n">
-        <v>6786922</v>
+        <v>6786991</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9143,22 +9143,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367665</v>
+        <v>129364474</v>
       </c>
       <c r="B87" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9166,37 +9166,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419522</v>
+        <v>419457</v>
       </c>
       <c r="R87" t="n">
-        <v>6786991</v>
+        <v>6787068</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9240,22 +9240,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129364474</v>
+        <v>129357097</v>
       </c>
       <c r="B88" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9263,21 +9263,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419457</v>
+        <v>419496</v>
       </c>
       <c r="R88" t="n">
-        <v>6787068</v>
+        <v>6786922</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9337,22 +9337,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129357093</v>
+        <v>129357128</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419453</v>
+        <v>419496</v>
       </c>
       <c r="R89" t="n">
-        <v>6786995</v>
+        <v>6787068</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9428,6 +9428,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9446,10 +9447,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129357128</v>
+        <v>129367670</v>
       </c>
       <c r="B90" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9477,17 +9478,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419496</v>
+        <v>419451</v>
       </c>
       <c r="R90" t="n">
-        <v>6787068</v>
+        <v>6787144</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9525,29 +9526,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357090</v>
+        <v>129357093</v>
       </c>
       <c r="B91" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419367</v>
+        <v>419453</v>
       </c>
       <c r="R91" t="n">
-        <v>6786988</v>
+        <v>6786995</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9641,10 +9641,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129367670</v>
+        <v>129357090</v>
       </c>
       <c r="B92" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9672,17 +9672,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419451</v>
+        <v>419367</v>
       </c>
       <c r="R92" t="n">
-        <v>6787144</v>
+        <v>6786988</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9726,12 +9726,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
         <v>129367654</v>
       </c>
       <c r="B93" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351462</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351476</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351439</v>
       </c>
       <c r="B4" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351440</v>
       </c>
       <c r="B5" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351455</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351471</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351464</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351475</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351461</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351458</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351459</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351469</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351472</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129351467</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351474</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351473</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351466</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351457</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129351438</v>
+        <v>129351465</v>
       </c>
       <c r="B20" t="n">
-        <v>78832</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419388</v>
+        <v>419384</v>
       </c>
       <c r="R20" t="n">
-        <v>6787098</v>
+        <v>6787088</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351465</v>
+        <v>129351460</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419384</v>
+        <v>419426</v>
       </c>
       <c r="R21" t="n">
-        <v>6787088</v>
+        <v>6787068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351460</v>
+        <v>129351438</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>78833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419426</v>
+        <v>419388</v>
       </c>
       <c r="R22" t="n">
-        <v>6787068</v>
+        <v>6787098</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
         <v>129351470</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351468</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129357115</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>129367678</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>129357114</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129357127</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>129357119</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>129357038</v>
       </c>
       <c r="B30" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129357110</v>
+        <v>129357111</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>419465</v>
+        <v>419456</v>
       </c>
       <c r="R31" t="n">
-        <v>6787134</v>
+        <v>6787149</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,10 +3816,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129357129</v>
+        <v>129357110</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>419416</v>
+        <v>419465</v>
       </c>
       <c r="R32" t="n">
-        <v>6787118</v>
+        <v>6787134</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3895,7 +3895,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3914,10 +3913,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129357111</v>
+        <v>129357096</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3949,10 +3948,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>419456</v>
+        <v>419433</v>
       </c>
       <c r="R33" t="n">
-        <v>6787149</v>
+        <v>6786954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4011,10 +4010,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129357096</v>
+        <v>129357129</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4046,10 +4045,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>419433</v>
+        <v>419416</v>
       </c>
       <c r="R34" t="n">
-        <v>6786954</v>
+        <v>6787118</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4090,6 +4089,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>129357107</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357105</v>
+        <v>129367674</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419505</v>
+        <v>419339</v>
       </c>
       <c r="R36" t="n">
-        <v>6787028</v>
+        <v>6787087</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,22 +4290,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357125</v>
+        <v>129357106</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419485</v>
+        <v>419505</v>
       </c>
       <c r="R37" t="n">
-        <v>6786929</v>
+        <v>6787037</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,7 +4381,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4400,10 +4399,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357091</v>
+        <v>129357123</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4435,10 +4434,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419411</v>
+        <v>419467</v>
       </c>
       <c r="R38" t="n">
-        <v>6786979</v>
+        <v>6787011</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,6 +4478,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129367674</v>
+        <v>129357105</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419339</v>
+        <v>419505</v>
       </c>
       <c r="R39" t="n">
-        <v>6787087</v>
+        <v>6787028</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,22 +4582,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357106</v>
+        <v>129357125</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419505</v>
+        <v>419485</v>
       </c>
       <c r="R40" t="n">
-        <v>6787037</v>
+        <v>6786929</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,6 +4673,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357123</v>
+        <v>129357091</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4726,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419467</v>
+        <v>419411</v>
       </c>
       <c r="R41" t="n">
-        <v>6787011</v>
+        <v>6786979</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4770,7 +4771,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>129357095</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>129357109</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>129364483</v>
       </c>
       <c r="B44" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>129367675</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>129357100</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>129357113</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364495</v>
+        <v>129364472</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419475</v>
+        <v>419439</v>
       </c>
       <c r="R48" t="n">
-        <v>6787178</v>
+        <v>6786970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5468,10 +5468,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364491</v>
+        <v>129364495</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419450</v>
+        <v>419475</v>
       </c>
       <c r="R49" t="n">
-        <v>6787079</v>
+        <v>6787178</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,10 +5565,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367679</v>
+        <v>129364491</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5596,17 +5596,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419258</v>
+        <v>419450</v>
       </c>
       <c r="R50" t="n">
-        <v>6787042</v>
+        <v>6787079</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367681</v>
+        <v>129367679</v>
       </c>
       <c r="B51" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419245</v>
+        <v>419258</v>
       </c>
       <c r="R51" t="n">
-        <v>6787037</v>
+        <v>6787042</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364472</v>
+        <v>129367681</v>
       </c>
       <c r="B52" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,37 +5770,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419439</v>
+        <v>419245</v>
       </c>
       <c r="R52" t="n">
-        <v>6786970</v>
+        <v>6787037</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5859,7 +5859,7 @@
         <v>129367652</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367619</v>
+        <v>129367657</v>
       </c>
       <c r="B54" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419457</v>
+        <v>419454</v>
       </c>
       <c r="R54" t="n">
-        <v>6787086</v>
+        <v>6787097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B55" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R55" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367657</v>
+        <v>129367619</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>78834</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419454</v>
+        <v>419457</v>
       </c>
       <c r="R56" t="n">
-        <v>6787097</v>
+        <v>6787086</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367668</v>
+        <v>129367607</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419481</v>
+        <v>419451</v>
       </c>
       <c r="R57" t="n">
-        <v>6787056</v>
+        <v>6787144</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6344,7 +6344,7 @@
         <v>129367666</v>
       </c>
       <c r="B58" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>129364497</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>129357103</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>129357092</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>129367680</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>129367669</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>129367663</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,10 +7020,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357121</v>
+        <v>129357126</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419244</v>
+        <v>419522</v>
       </c>
       <c r="R65" t="n">
-        <v>6787051</v>
+        <v>6786923</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7099,6 +7099,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7117,10 +7118,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357126</v>
+        <v>129357121</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7152,10 +7153,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419522</v>
+        <v>419244</v>
       </c>
       <c r="R66" t="n">
-        <v>6786923</v>
+        <v>6787051</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7196,7 +7197,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>129367655</v>
       </c>
       <c r="B67" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>129367676</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7409,10 +7409,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129367656</v>
+        <v>129357094</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419497</v>
+        <v>419463</v>
       </c>
       <c r="R69" t="n">
-        <v>6787027</v>
+        <v>6786985</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,22 +7494,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129367653</v>
+        <v>129367656</v>
       </c>
       <c r="B70" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419288</v>
+        <v>419497</v>
       </c>
       <c r="R70" t="n">
-        <v>6787048</v>
+        <v>6787027</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7603,10 +7603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129364493</v>
+        <v>129367653</v>
       </c>
       <c r="B71" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7634,17 +7634,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419438</v>
+        <v>419288</v>
       </c>
       <c r="R71" t="n">
-        <v>6787138</v>
+        <v>6787048</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7688,22 +7688,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367664</v>
+        <v>129364493</v>
       </c>
       <c r="B72" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7731,17 +7731,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419363</v>
+        <v>419438</v>
       </c>
       <c r="R72" t="n">
-        <v>6787023</v>
+        <v>6787138</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7785,22 +7785,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129357094</v>
+        <v>129367664</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7828,17 +7828,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419463</v>
+        <v>419363</v>
       </c>
       <c r="R73" t="n">
-        <v>6786985</v>
+        <v>6787023</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7882,12 +7882,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7897,7 +7897,7 @@
         <v>129367651</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>129357120</v>
       </c>
       <c r="B75" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>129357118</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>129357099</v>
       </c>
       <c r="B77" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>129357117</v>
       </c>
       <c r="B78" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>129367677</v>
       </c>
       <c r="B79" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>129367658</v>
       </c>
       <c r="B80" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129364490</v>
       </c>
       <c r="B81" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>129367662</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>129367673</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>129357108</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>129357102</v>
       </c>
       <c r="B85" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129367665</v>
+        <v>129357097</v>
       </c>
       <c r="B86" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9089,17 +9089,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419522</v>
+        <v>419496</v>
       </c>
       <c r="R86" t="n">
-        <v>6786991</v>
+        <v>6786922</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9143,22 +9143,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129364474</v>
+        <v>129367665</v>
       </c>
       <c r="B87" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9166,37 +9166,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419457</v>
+        <v>419522</v>
       </c>
       <c r="R87" t="n">
-        <v>6787068</v>
+        <v>6786991</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9240,22 +9240,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129357097</v>
+        <v>129364474</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9263,21 +9263,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419496</v>
+        <v>419457</v>
       </c>
       <c r="R88" t="n">
-        <v>6786922</v>
+        <v>6787068</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9337,22 +9337,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129357128</v>
+        <v>129367672</v>
       </c>
       <c r="B89" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9380,17 +9380,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>419496</v>
+        <v>419451</v>
       </c>
       <c r="R89" t="n">
-        <v>6787068</v>
+        <v>6787144</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9428,29 +9428,28 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129367670</v>
+        <v>129357090</v>
       </c>
       <c r="B90" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9478,17 +9477,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>419451</v>
+        <v>419367</v>
       </c>
       <c r="R90" t="n">
-        <v>6787144</v>
+        <v>6786988</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9532,22 +9531,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129357093</v>
+        <v>129357128</v>
       </c>
       <c r="B91" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9579,10 +9578,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>419453</v>
+        <v>419496</v>
       </c>
       <c r="R91" t="n">
-        <v>6786995</v>
+        <v>6787068</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9623,6 +9622,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9641,10 +9641,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129357090</v>
+        <v>129357093</v>
       </c>
       <c r="B92" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>419367</v>
+        <v>419453</v>
       </c>
       <c r="R92" t="n">
-        <v>6786988</v>
+        <v>6786995</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9741,7 +9741,7 @@
         <v>129367654</v>
       </c>
       <c r="B93" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -4205,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129367674</v>
+        <v>129357105</v>
       </c>
       <c r="B36" t="n">
         <v>79076</v>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419339</v>
+        <v>419505</v>
       </c>
       <c r="R36" t="n">
-        <v>6787087</v>
+        <v>6787028</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,19 +4290,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357106</v>
+        <v>129357125</v>
       </c>
       <c r="B37" t="n">
         <v>79076</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419505</v>
+        <v>419485</v>
       </c>
       <c r="R37" t="n">
-        <v>6787037</v>
+        <v>6786929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,6 +4381,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,7 +4400,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357123</v>
+        <v>129357091</v>
       </c>
       <c r="B38" t="n">
         <v>79076</v>
@@ -4434,10 +4435,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419467</v>
+        <v>419411</v>
       </c>
       <c r="R38" t="n">
-        <v>6787011</v>
+        <v>6786979</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,7 +4479,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357105</v>
+        <v>129367674</v>
       </c>
       <c r="B39" t="n">
         <v>79076</v>
@@ -4528,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419505</v>
+        <v>419339</v>
       </c>
       <c r="R39" t="n">
-        <v>6787028</v>
+        <v>6787087</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,19 +4582,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357125</v>
+        <v>129357106</v>
       </c>
       <c r="B40" t="n">
         <v>79076</v>
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419485</v>
+        <v>419505</v>
       </c>
       <c r="R40" t="n">
-        <v>6786929</v>
+        <v>6787037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,7 +4673,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4692,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357091</v>
+        <v>129357123</v>
       </c>
       <c r="B41" t="n">
         <v>79076</v>
@@ -4727,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419411</v>
+        <v>419467</v>
       </c>
       <c r="R41" t="n">
-        <v>6786979</v>
+        <v>6787011</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,6 +4770,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129357095</v>
+        <v>129364483</v>
       </c>
       <c r="B42" t="n">
-        <v>79076</v>
+        <v>78833</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419457</v>
+        <v>419459</v>
       </c>
       <c r="R42" t="n">
-        <v>6786992</v>
+        <v>6786999</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,19 +4874,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357109</v>
+        <v>129357095</v>
       </c>
       <c r="B43" t="n">
         <v>79076</v>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419470</v>
+        <v>419457</v>
       </c>
       <c r="R43" t="n">
-        <v>6787115</v>
+        <v>6786992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129364483</v>
+        <v>129357109</v>
       </c>
       <c r="B44" t="n">
-        <v>78833</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419459</v>
+        <v>419470</v>
       </c>
       <c r="R44" t="n">
-        <v>6786999</v>
+        <v>6787115</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,12 +5068,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364472</v>
+        <v>129364495</v>
       </c>
       <c r="B48" t="n">
-        <v>79695</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419439</v>
+        <v>419475</v>
       </c>
       <c r="R48" t="n">
-        <v>6786970</v>
+        <v>6787178</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364495</v>
+        <v>129364491</v>
       </c>
       <c r="B49" t="n">
         <v>79076</v>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419475</v>
+        <v>419450</v>
       </c>
       <c r="R49" t="n">
-        <v>6787178</v>
+        <v>6787079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129364491</v>
+        <v>129367679</v>
       </c>
       <c r="B50" t="n">
         <v>79076</v>
@@ -5596,17 +5596,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419450</v>
+        <v>419258</v>
       </c>
       <c r="R50" t="n">
-        <v>6787079</v>
+        <v>6787042</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,19 +5650,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367679</v>
+        <v>129367681</v>
       </c>
       <c r="B51" t="n">
         <v>79076</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419258</v>
+        <v>419245</v>
       </c>
       <c r="R51" t="n">
-        <v>6787042</v>
+        <v>6787037</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367681</v>
+        <v>129364472</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>79695</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,37 +5770,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419245</v>
+        <v>419439</v>
       </c>
       <c r="R52" t="n">
-        <v>6787037</v>
+        <v>6786970</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367657</v>
+        <v>129367619</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>78834</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419454</v>
+        <v>419457</v>
       </c>
       <c r="R54" t="n">
-        <v>6787097</v>
+        <v>6787086</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367668</v>
+        <v>129367607</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419481</v>
+        <v>419451</v>
       </c>
       <c r="R55" t="n">
-        <v>6787056</v>
+        <v>6787144</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367619</v>
+        <v>129367657</v>
       </c>
       <c r="B56" t="n">
-        <v>78834</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419457</v>
+        <v>419454</v>
       </c>
       <c r="R56" t="n">
-        <v>6787086</v>
+        <v>6787097</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B57" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R57" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7312,7 +7312,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367676</v>
+        <v>129357094</v>
       </c>
       <c r="B68" t="n">
         <v>79076</v>
@@ -7343,17 +7343,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419277</v>
+        <v>419463</v>
       </c>
       <c r="R68" t="n">
-        <v>6787033</v>
+        <v>6786985</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7397,19 +7397,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357094</v>
+        <v>129367656</v>
       </c>
       <c r="B69" t="n">
         <v>79076</v>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419463</v>
+        <v>419497</v>
       </c>
       <c r="R69" t="n">
-        <v>6786985</v>
+        <v>6787027</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,19 +7494,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129367656</v>
+        <v>129367653</v>
       </c>
       <c r="B70" t="n">
         <v>79076</v>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419497</v>
+        <v>419288</v>
       </c>
       <c r="R70" t="n">
-        <v>6787027</v>
+        <v>6787048</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367653</v>
+        <v>129364493</v>
       </c>
       <c r="B71" t="n">
         <v>79076</v>
@@ -7634,17 +7634,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419288</v>
+        <v>419438</v>
       </c>
       <c r="R71" t="n">
-        <v>6787048</v>
+        <v>6787138</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7688,19 +7688,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129364493</v>
+        <v>129367664</v>
       </c>
       <c r="B72" t="n">
         <v>79076</v>
@@ -7731,17 +7731,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419438</v>
+        <v>419363</v>
       </c>
       <c r="R72" t="n">
-        <v>6787138</v>
+        <v>6787023</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367664</v>
+        <v>129367651</v>
       </c>
       <c r="B73" t="n">
         <v>79076</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419363</v>
+        <v>419250</v>
       </c>
       <c r="R73" t="n">
-        <v>6787023</v>
+        <v>6787043</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367651</v>
+        <v>129367676</v>
       </c>
       <c r="B74" t="n">
         <v>79076</v>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419250</v>
+        <v>419277</v>
       </c>
       <c r="R74" t="n">
-        <v>6787043</v>
+        <v>6787033</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351462</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129351476</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129351439</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129351440</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129351455</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129351471</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129351464</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>129351475</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>129351461</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>129351458</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129351459</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>129351469</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>129351472</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>129351467</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129351474</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129351473</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129351466</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129351457</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129351465</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351460</v>
+        <v>129351438</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419426</v>
+        <v>419388</v>
       </c>
       <c r="R21" t="n">
-        <v>6787068</v>
+        <v>6787098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351438</v>
+        <v>129351460</v>
       </c>
       <c r="B22" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>419388</v>
+        <v>419426</v>
       </c>
       <c r="R22" t="n">
-        <v>6787098</v>
+        <v>6787068</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
         <v>129351470</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>129351468</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129357115</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>129367678</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129357114</v>
+        <v>129357127</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419458</v>
+        <v>419531</v>
       </c>
       <c r="R27" t="n">
-        <v>6787193</v>
+        <v>6786974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,6 +3409,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3427,10 +3428,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357127</v>
+        <v>129357114</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3462,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419531</v>
+        <v>419458</v>
       </c>
       <c r="R28" t="n">
-        <v>6786974</v>
+        <v>6787193</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,7 +3507,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>129357119</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>129357111</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>129357110</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>129357096</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129357129</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>129357107</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357105</v>
+        <v>129367674</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419505</v>
+        <v>419339</v>
       </c>
       <c r="R36" t="n">
-        <v>6787028</v>
+        <v>6787087</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,22 +4290,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357125</v>
+        <v>129357105</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419485</v>
+        <v>419505</v>
       </c>
       <c r="R37" t="n">
-        <v>6786929</v>
+        <v>6787028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,7 +4381,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4400,10 +4399,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357091</v>
+        <v>129357125</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4435,10 +4434,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419411</v>
+        <v>419485</v>
       </c>
       <c r="R38" t="n">
-        <v>6786979</v>
+        <v>6786929</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4479,6 +4478,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129367674</v>
+        <v>129357091</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419339</v>
+        <v>419411</v>
       </c>
       <c r="R39" t="n">
-        <v>6787087</v>
+        <v>6786979</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4597,7 +4597,7 @@
         <v>129357106</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>129357123</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129364483</v>
+        <v>129357095</v>
       </c>
       <c r="B42" t="n">
-        <v>78833</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419459</v>
+        <v>419457</v>
       </c>
       <c r="R42" t="n">
-        <v>6786999</v>
+        <v>6786992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,22 +4874,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357095</v>
+        <v>129357109</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419457</v>
+        <v>419470</v>
       </c>
       <c r="R43" t="n">
-        <v>6786992</v>
+        <v>6787115</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357109</v>
+        <v>129364483</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419470</v>
+        <v>419459</v>
       </c>
       <c r="R44" t="n">
-        <v>6787115</v>
+        <v>6786999</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,22 +5068,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129367675</v>
+        <v>129357100</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5111,17 +5111,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419314</v>
+        <v>419525</v>
       </c>
       <c r="R45" t="n">
-        <v>6787092</v>
+        <v>6787008</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,22 +5165,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129357100</v>
+        <v>129367675</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5208,17 +5208,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419525</v>
+        <v>419314</v>
       </c>
       <c r="R46" t="n">
-        <v>6787008</v>
+        <v>6787092</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,12 +5262,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5277,7 +5277,7 @@
         <v>129357113</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364495</v>
+        <v>129367679</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,17 +5402,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419475</v>
+        <v>419258</v>
       </c>
       <c r="R48" t="n">
-        <v>6787178</v>
+        <v>6787042</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5456,12 +5456,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5471,7 +5471,7 @@
         <v>129364491</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367679</v>
+        <v>129364472</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>79700</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5576,37 +5576,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419258</v>
+        <v>419439</v>
       </c>
       <c r="R50" t="n">
-        <v>6787042</v>
+        <v>6786970</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,12 +5650,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5665,7 +5665,7 @@
         <v>129367681</v>
       </c>
       <c r="B51" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5752,17 +5752,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364472</v>
+        <v>129364495</v>
       </c>
       <c r="B52" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,21 +5770,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419439</v>
+        <v>419475</v>
       </c>
       <c r="R52" t="n">
-        <v>6786970</v>
+        <v>6787178</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5859,7 +5859,7 @@
         <v>129367652</v>
       </c>
       <c r="B53" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
         <v>129367619</v>
       </c>
       <c r="B54" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>129367607</v>
       </c>
       <c r="B55" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6140,17 +6140,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367657</v>
+        <v>129367668</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419454</v>
+        <v>419481</v>
       </c>
       <c r="R56" t="n">
-        <v>6787097</v>
+        <v>6787056</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6237,17 +6237,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367668</v>
+        <v>129367657</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419481</v>
+        <v>419454</v>
       </c>
       <c r="R57" t="n">
-        <v>6787056</v>
+        <v>6787097</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6334,17 +6334,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129367666</v>
+        <v>129367680</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419496</v>
+        <v>419248</v>
       </c>
       <c r="R58" t="n">
-        <v>6787020</v>
+        <v>6787041</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6431,17 +6431,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129364497</v>
+        <v>129367666</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6469,17 +6469,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419476</v>
+        <v>419496</v>
       </c>
       <c r="R59" t="n">
-        <v>6787193</v>
+        <v>6787020</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6523,22 +6523,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129357103</v>
+        <v>129364497</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419509</v>
+        <v>419476</v>
       </c>
       <c r="R60" t="n">
-        <v>6787026</v>
+        <v>6787193</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,22 +6620,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357092</v>
+        <v>129357103</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419418</v>
+        <v>419509</v>
       </c>
       <c r="R61" t="n">
-        <v>6786979</v>
+        <v>6787026</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6729,10 +6729,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129367680</v>
+        <v>129357092</v>
       </c>
       <c r="B62" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6760,17 +6760,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419248</v>
+        <v>419418</v>
       </c>
       <c r="R62" t="n">
-        <v>6787041</v>
+        <v>6786979</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6814,22 +6814,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367669</v>
+        <v>129367663</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419463</v>
+        <v>419353</v>
       </c>
       <c r="R63" t="n">
-        <v>6787067</v>
+        <v>6787020</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6916,17 +6916,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129367663</v>
+        <v>129357126</v>
       </c>
       <c r="B64" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6954,17 +6954,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419353</v>
+        <v>419522</v>
       </c>
       <c r="R64" t="n">
-        <v>6787020</v>
+        <v>6786923</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7002,28 +7002,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357126</v>
+        <v>129367669</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7051,17 +7052,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419522</v>
+        <v>419463</v>
       </c>
       <c r="R65" t="n">
-        <v>6786923</v>
+        <v>6787067</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7099,19 +7100,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7121,7 +7121,7 @@
         <v>129357121</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>129367655</v>
       </c>
       <c r="B67" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7305,17 +7305,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129357094</v>
+        <v>129367656</v>
       </c>
       <c r="B68" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7343,17 +7343,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419463</v>
+        <v>419497</v>
       </c>
       <c r="R68" t="n">
-        <v>6786985</v>
+        <v>6787027</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7397,22 +7397,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129367656</v>
+        <v>129367653</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419497</v>
+        <v>419288</v>
       </c>
       <c r="R69" t="n">
-        <v>6787027</v>
+        <v>6787048</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7499,17 +7499,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129367653</v>
+        <v>129364493</v>
       </c>
       <c r="B70" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7537,17 +7537,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419288</v>
+        <v>419438</v>
       </c>
       <c r="R70" t="n">
-        <v>6787048</v>
+        <v>6787138</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7591,22 +7591,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129364493</v>
+        <v>129367664</v>
       </c>
       <c r="B71" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7634,17 +7634,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419438</v>
+        <v>419363</v>
       </c>
       <c r="R71" t="n">
-        <v>6787138</v>
+        <v>6787023</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7688,22 +7688,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367664</v>
+        <v>129367651</v>
       </c>
       <c r="B72" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419363</v>
+        <v>419250</v>
       </c>
       <c r="R72" t="n">
-        <v>6787023</v>
+        <v>6787043</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7790,17 +7790,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367651</v>
+        <v>129367676</v>
       </c>
       <c r="B73" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419250</v>
+        <v>419277</v>
       </c>
       <c r="R73" t="n">
-        <v>6787043</v>
+        <v>6787033</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7887,17 +7887,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367676</v>
+        <v>129357094</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7925,17 +7925,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419277</v>
+        <v>419463</v>
       </c>
       <c r="R74" t="n">
-        <v>6787033</v>
+        <v>6786985</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7979,12 +7979,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7994,7 +7994,7 @@
         <v>129357120</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>129357118</v>
       </c>
       <c r="B76" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>129357099</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>129357117</v>
       </c>
       <c r="B78" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>129367677</v>
       </c>
       <c r="B79" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8479,7 +8479,7 @@
         <v>129367658</v>
       </c>
       <c r="B80" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8576,7 +8576,7 @@
         <v>129364490</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>129367662</v>
       </c>
       <c r="B82" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8770,7 +8770,7 @@
         <v>129367673</v>
       </c>
       <c r="B83" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8867,7 +8867,7 @@
         <v>129357108</v>
       </c>
       <c r="B84" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>129357102</v>
       </c>
       <c r="B85" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>129357097</v>
       </c>
       <c r="B86" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>129367665</v>
       </c>
       <c r="B87" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9255,7 +9255,7 @@
         <v>129364474</v>
       </c>
       <c r="B88" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>129367672</v>
       </c>
       <c r="B89" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9449,7 +9449,7 @@
         <v>129357090</v>
       </c>
       <c r="B90" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>129357128</v>
       </c>
       <c r="B91" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>129357093</v>
       </c>
       <c r="B92" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>129367654</v>
       </c>
       <c r="B93" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -3323,14 +3323,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129357127</v>
+        <v>129357114</v>
       </c>
       <c r="B27" t="n">
         <v>79081</v>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>419531</v>
+        <v>419458</v>
       </c>
       <c r="R27" t="n">
-        <v>6786974</v>
+        <v>6787193</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,7 +3409,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3428,7 +3427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129357114</v>
+        <v>129357127</v>
       </c>
       <c r="B28" t="n">
         <v>79081</v>
@@ -3463,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>419458</v>
+        <v>419531</v>
       </c>
       <c r="R28" t="n">
-        <v>6787193</v>
+        <v>6786974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3507,6 +3506,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129367674</v>
+        <v>129357105</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419339</v>
+        <v>419505</v>
       </c>
       <c r="R36" t="n">
-        <v>6787087</v>
+        <v>6787028</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,19 +4290,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357105</v>
+        <v>129357125</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419505</v>
+        <v>419485</v>
       </c>
       <c r="R37" t="n">
-        <v>6787028</v>
+        <v>6786929</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,6 +4381,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4399,7 +4400,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357125</v>
+        <v>129357091</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4434,10 +4435,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419485</v>
+        <v>419411</v>
       </c>
       <c r="R38" t="n">
-        <v>6786929</v>
+        <v>6786979</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,7 +4479,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357091</v>
+        <v>129367674</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4528,17 +4528,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419411</v>
+        <v>419339</v>
       </c>
       <c r="R39" t="n">
-        <v>6786979</v>
+        <v>6787087</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,12 +4582,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129357100</v>
+        <v>129367675</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5111,17 +5111,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>419525</v>
+        <v>419314</v>
       </c>
       <c r="R45" t="n">
-        <v>6787008</v>
+        <v>6787092</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5165,19 +5165,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129367675</v>
+        <v>129357100</v>
       </c>
       <c r="B46" t="n">
         <v>79081</v>
@@ -5208,17 +5208,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>419314</v>
+        <v>419525</v>
       </c>
       <c r="R46" t="n">
-        <v>6787092</v>
+        <v>6787008</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5262,12 +5262,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5371,7 +5371,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129367679</v>
+        <v>129364495</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5402,17 +5402,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419258</v>
+        <v>419475</v>
       </c>
       <c r="R48" t="n">
-        <v>6787042</v>
+        <v>6787178</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5456,12 +5456,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5565,10 +5565,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129364472</v>
+        <v>129367679</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5576,37 +5576,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419439</v>
+        <v>419258</v>
       </c>
       <c r="R50" t="n">
-        <v>6786970</v>
+        <v>6787042</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129367681</v>
+        <v>129364472</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,37 +5673,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419245</v>
+        <v>419439</v>
       </c>
       <c r="R51" t="n">
-        <v>6787037</v>
+        <v>6786970</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5747,19 +5747,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129364495</v>
+        <v>129367681</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5790,17 +5790,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419475</v>
+        <v>419245</v>
       </c>
       <c r="R52" t="n">
-        <v>6787178</v>
+        <v>6787037</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5946,17 +5946,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367619</v>
+        <v>129367657</v>
       </c>
       <c r="B54" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419457</v>
+        <v>419454</v>
       </c>
       <c r="R54" t="n">
-        <v>6787086</v>
+        <v>6787097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B55" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R55" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6140,17 +6140,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367668</v>
+        <v>129367619</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419481</v>
+        <v>419457</v>
       </c>
       <c r="R56" t="n">
-        <v>6787056</v>
+        <v>6787086</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6237,17 +6237,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367657</v>
+        <v>129367607</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419454</v>
+        <v>419451</v>
       </c>
       <c r="R57" t="n">
-        <v>6787097</v>
+        <v>6787144</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6334,14 +6334,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129367680</v>
+        <v>129367666</v>
       </c>
       <c r="B58" t="n">
         <v>79081</v>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>419248</v>
+        <v>419496</v>
       </c>
       <c r="R58" t="n">
-        <v>6787041</v>
+        <v>6787020</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6431,14 +6431,14 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129367666</v>
+        <v>129364497</v>
       </c>
       <c r="B59" t="n">
         <v>79081</v>
@@ -6469,17 +6469,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>419496</v>
+        <v>419476</v>
       </c>
       <c r="R59" t="n">
-        <v>6787020</v>
+        <v>6787193</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6523,19 +6523,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129364497</v>
+        <v>129357103</v>
       </c>
       <c r="B60" t="n">
         <v>79081</v>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>419476</v>
+        <v>419509</v>
       </c>
       <c r="R60" t="n">
-        <v>6787193</v>
+        <v>6787026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,19 +6620,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129357103</v>
+        <v>129357092</v>
       </c>
       <c r="B61" t="n">
         <v>79081</v>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>419509</v>
+        <v>419418</v>
       </c>
       <c r="R61" t="n">
-        <v>6787026</v>
+        <v>6786979</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129357092</v>
+        <v>129367680</v>
       </c>
       <c r="B62" t="n">
         <v>79081</v>
@@ -6760,17 +6760,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>419418</v>
+        <v>419248</v>
       </c>
       <c r="R62" t="n">
-        <v>6786979</v>
+        <v>6787041</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6814,19 +6814,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129367663</v>
+        <v>129367669</v>
       </c>
       <c r="B63" t="n">
         <v>79081</v>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>419353</v>
+        <v>419463</v>
       </c>
       <c r="R63" t="n">
-        <v>6787020</v>
+        <v>6787067</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129357126</v>
+        <v>129367663</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6954,17 +6954,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419522</v>
+        <v>419353</v>
       </c>
       <c r="R64" t="n">
-        <v>6786923</v>
+        <v>6787020</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7002,26 +7002,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129367669</v>
+        <v>129357126</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7052,17 +7051,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419463</v>
+        <v>419522</v>
       </c>
       <c r="R65" t="n">
-        <v>6787067</v>
+        <v>6786923</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7100,18 +7099,19 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367656</v>
+        <v>129367676</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419497</v>
+        <v>419277</v>
       </c>
       <c r="R68" t="n">
-        <v>6787027</v>
+        <v>6787033</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7402,14 +7402,14 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129367653</v>
+        <v>129357094</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419288</v>
+        <v>419463</v>
       </c>
       <c r="R69" t="n">
-        <v>6787048</v>
+        <v>6786985</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,19 +7494,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129364493</v>
+        <v>129367656</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7537,17 +7537,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419438</v>
+        <v>419497</v>
       </c>
       <c r="R70" t="n">
-        <v>6787138</v>
+        <v>6787027</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7591,19 +7591,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367664</v>
+        <v>129367653</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419363</v>
+        <v>419288</v>
       </c>
       <c r="R71" t="n">
-        <v>6787023</v>
+        <v>6787048</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7693,14 +7693,14 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129367651</v>
+        <v>129364493</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7731,17 +7731,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419250</v>
+        <v>419438</v>
       </c>
       <c r="R72" t="n">
-        <v>6787043</v>
+        <v>6787138</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367676</v>
+        <v>129367664</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419277</v>
+        <v>419363</v>
       </c>
       <c r="R73" t="n">
-        <v>6787033</v>
+        <v>6787023</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7887,14 +7887,14 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129357094</v>
+        <v>129367651</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -7925,17 +7925,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419463</v>
+        <v>419250</v>
       </c>
       <c r="R74" t="n">
-        <v>6786985</v>
+        <v>6787043</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7979,12 +7979,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129351465</v>
+        <v>129351438</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>419384</v>
+        <v>419388</v>
       </c>
       <c r="R20" t="n">
-        <v>6787088</v>
+        <v>6787098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351438</v>
+        <v>129351465</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>419388</v>
+        <v>419384</v>
       </c>
       <c r="R21" t="n">
-        <v>6787098</v>
+        <v>6787088</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4302,7 +4302,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357125</v>
+        <v>129357091</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419485</v>
+        <v>419411</v>
       </c>
       <c r="R37" t="n">
-        <v>6786929</v>
+        <v>6786979</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4381,7 +4381,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4400,7 +4399,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129357091</v>
+        <v>129367674</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4431,17 +4430,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419411</v>
+        <v>419339</v>
       </c>
       <c r="R38" t="n">
-        <v>6786979</v>
+        <v>6787087</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4485,19 +4484,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129367674</v>
+        <v>129357106</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4528,17 +4527,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419339</v>
+        <v>419505</v>
       </c>
       <c r="R39" t="n">
-        <v>6787087</v>
+        <v>6787037</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4582,19 +4581,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357106</v>
+        <v>129357123</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4629,10 +4628,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419505</v>
+        <v>419467</v>
       </c>
       <c r="R40" t="n">
-        <v>6787037</v>
+        <v>6787011</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,6 +4672,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357123</v>
+        <v>129357125</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419467</v>
+        <v>419485</v>
       </c>
       <c r="R41" t="n">
-        <v>6787011</v>
+        <v>6786929</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129357095</v>
+        <v>129364483</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419457</v>
+        <v>419459</v>
       </c>
       <c r="R42" t="n">
-        <v>6786992</v>
+        <v>6786999</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,19 +4874,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357109</v>
+        <v>129357095</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419470</v>
+        <v>419457</v>
       </c>
       <c r="R43" t="n">
-        <v>6787115</v>
+        <v>6786992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129364483</v>
+        <v>129357109</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419459</v>
+        <v>419470</v>
       </c>
       <c r="R44" t="n">
-        <v>6786999</v>
+        <v>6787115</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,12 +5068,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364495</v>
+        <v>129364472</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,21 +5382,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419475</v>
+        <v>419439</v>
       </c>
       <c r="R48" t="n">
-        <v>6787178</v>
+        <v>6786970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5468,7 +5468,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129364491</v>
+        <v>129364495</v>
       </c>
       <c r="B49" t="n">
         <v>79081</v>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>419450</v>
+        <v>419475</v>
       </c>
       <c r="R49" t="n">
-        <v>6787079</v>
+        <v>6787178</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129367679</v>
+        <v>129364491</v>
       </c>
       <c r="B50" t="n">
         <v>79081</v>
@@ -5596,17 +5596,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>419258</v>
+        <v>419450</v>
       </c>
       <c r="R50" t="n">
-        <v>6787042</v>
+        <v>6787079</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129364472</v>
+        <v>129367679</v>
       </c>
       <c r="B51" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5673,37 +5673,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>419439</v>
+        <v>419258</v>
       </c>
       <c r="R51" t="n">
-        <v>6786970</v>
+        <v>6787042</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5747,12 +5747,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367657</v>
+        <v>129367619</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419454</v>
+        <v>419457</v>
       </c>
       <c r="R54" t="n">
-        <v>6787097</v>
+        <v>6787086</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367668</v>
+        <v>129367607</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419481</v>
+        <v>419451</v>
       </c>
       <c r="R55" t="n">
-        <v>6787056</v>
+        <v>6787144</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367619</v>
+        <v>129367657</v>
       </c>
       <c r="B56" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419457</v>
+        <v>419454</v>
       </c>
       <c r="R56" t="n">
-        <v>6787086</v>
+        <v>6787097</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B57" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R57" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129357097</v>
+        <v>129364474</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9069,21 +9069,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419496</v>
+        <v>419457</v>
       </c>
       <c r="R86" t="n">
-        <v>6786922</v>
+        <v>6787068</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9143,19 +9143,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129367665</v>
+        <v>129357097</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9186,17 +9186,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419522</v>
+        <v>419496</v>
       </c>
       <c r="R87" t="n">
-        <v>6786991</v>
+        <v>6786922</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9240,22 +9240,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129364474</v>
+        <v>129367665</v>
       </c>
       <c r="B88" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9263,37 +9263,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419457</v>
+        <v>419522</v>
       </c>
       <c r="R88" t="n">
-        <v>6787068</v>
+        <v>6786991</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9337,12 +9337,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 46305-2025 artfynd.xlsx
+++ b/artfynd/A 46305-2025 artfynd.xlsx
@@ -4205,7 +4205,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129357105</v>
+        <v>129367674</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4236,17 +4236,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>419505</v>
+        <v>419339</v>
       </c>
       <c r="R36" t="n">
-        <v>6787028</v>
+        <v>6787087</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4290,19 +4290,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129357091</v>
+        <v>129357105</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>419411</v>
+        <v>419505</v>
       </c>
       <c r="R37" t="n">
-        <v>6786979</v>
+        <v>6787028</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129367674</v>
+        <v>129357125</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4430,17 +4430,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>419339</v>
+        <v>419485</v>
       </c>
       <c r="R38" t="n">
-        <v>6787087</v>
+        <v>6786929</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4478,25 +4478,26 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129357106</v>
+        <v>129357091</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4531,10 +4532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>419505</v>
+        <v>419411</v>
       </c>
       <c r="R39" t="n">
-        <v>6787037</v>
+        <v>6786979</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4593,7 +4594,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129357123</v>
+        <v>129357106</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4628,10 +4629,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>419467</v>
+        <v>419505</v>
       </c>
       <c r="R40" t="n">
-        <v>6787011</v>
+        <v>6787037</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4672,7 +4673,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129357125</v>
+        <v>129357123</v>
       </c>
       <c r="B41" t="n">
         <v>79081</v>
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>419485</v>
+        <v>419467</v>
       </c>
       <c r="R41" t="n">
-        <v>6786929</v>
+        <v>6787011</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129364483</v>
+        <v>129357095</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>419459</v>
+        <v>419457</v>
       </c>
       <c r="R42" t="n">
-        <v>6786999</v>
+        <v>6786992</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4874,19 +4874,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129357095</v>
+        <v>129357109</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>419457</v>
+        <v>419470</v>
       </c>
       <c r="R43" t="n">
-        <v>6786992</v>
+        <v>6787115</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129357109</v>
+        <v>129364483</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>419470</v>
+        <v>419459</v>
       </c>
       <c r="R44" t="n">
-        <v>6787115</v>
+        <v>6786999</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,12 +5068,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129364472</v>
+        <v>129367681</v>
       </c>
       <c r="B48" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5382,37 +5382,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>419439</v>
+        <v>419245</v>
       </c>
       <c r="R48" t="n">
-        <v>6786970</v>
+        <v>6787037</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5456,12 +5456,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129367681</v>
+        <v>129364472</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5770,37 +5770,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>419245</v>
+        <v>419439</v>
       </c>
       <c r="R52" t="n">
-        <v>6787037</v>
+        <v>6786970</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5844,12 +5844,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129367619</v>
+        <v>129367657</v>
       </c>
       <c r="B54" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>419457</v>
+        <v>419454</v>
       </c>
       <c r="R54" t="n">
-        <v>6787086</v>
+        <v>6787097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129367607</v>
+        <v>129367668</v>
       </c>
       <c r="B55" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>419451</v>
+        <v>419481</v>
       </c>
       <c r="R55" t="n">
-        <v>6787144</v>
+        <v>6787056</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129367657</v>
+        <v>129367619</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>419454</v>
+        <v>419457</v>
       </c>
       <c r="R56" t="n">
-        <v>6787097</v>
+        <v>6787086</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129367668</v>
+        <v>129367607</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>419481</v>
+        <v>419451</v>
       </c>
       <c r="R57" t="n">
-        <v>6787056</v>
+        <v>6787144</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129367663</v>
+        <v>129357126</v>
       </c>
       <c r="B64" t="n">
         <v>79081</v>
@@ -6954,17 +6954,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>419353</v>
+        <v>419522</v>
       </c>
       <c r="R64" t="n">
-        <v>6787020</v>
+        <v>6786923</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7002,25 +7002,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129357126</v>
+        <v>129357121</v>
       </c>
       <c r="B65" t="n">
         <v>79081</v>
@@ -7055,10 +7056,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>419522</v>
+        <v>419244</v>
       </c>
       <c r="R65" t="n">
-        <v>6786923</v>
+        <v>6787051</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7099,7 +7100,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7118,7 +7118,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129357121</v>
+        <v>129367663</v>
       </c>
       <c r="B66" t="n">
         <v>79081</v>
@@ -7149,17 +7149,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>419244</v>
+        <v>419353</v>
       </c>
       <c r="R66" t="n">
-        <v>6787051</v>
+        <v>6787020</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7203,19 +7203,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129367655</v>
+        <v>129364493</v>
       </c>
       <c r="B67" t="n">
         <v>79081</v>
@@ -7246,17 +7246,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>419317</v>
+        <v>419438</v>
       </c>
       <c r="R67" t="n">
-        <v>6787029</v>
+        <v>6787138</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7300,19 +7300,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129367676</v>
+        <v>129367655</v>
       </c>
       <c r="B68" t="n">
         <v>79081</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>419277</v>
+        <v>419317</v>
       </c>
       <c r="R68" t="n">
-        <v>6787033</v>
+        <v>6787029</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129357094</v>
+        <v>129367676</v>
       </c>
       <c r="B69" t="n">
         <v>79081</v>
@@ -7440,17 +7440,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>419463</v>
+        <v>419277</v>
       </c>
       <c r="R69" t="n">
-        <v>6786985</v>
+        <v>6787033</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7494,19 +7494,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129367656</v>
+        <v>129357094</v>
       </c>
       <c r="B70" t="n">
         <v>79081</v>
@@ -7537,17 +7537,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>419497</v>
+        <v>419463</v>
       </c>
       <c r="R70" t="n">
-        <v>6787027</v>
+        <v>6786985</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7591,19 +7591,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129367653</v>
+        <v>129367656</v>
       </c>
       <c r="B71" t="n">
         <v>79081</v>
@@ -7638,10 +7638,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>419288</v>
+        <v>419497</v>
       </c>
       <c r="R71" t="n">
-        <v>6787048</v>
+        <v>6787027</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7700,7 +7700,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129364493</v>
+        <v>129367653</v>
       </c>
       <c r="B72" t="n">
         <v>79081</v>
@@ -7731,17 +7731,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>419438</v>
+        <v>419288</v>
       </c>
       <c r="R72" t="n">
-        <v>6787138</v>
+        <v>6787048</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7785,19 +7785,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129367664</v>
+        <v>129367651</v>
       </c>
       <c r="B73" t="n">
         <v>79081</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>419363</v>
+        <v>419250</v>
       </c>
       <c r="R73" t="n">
-        <v>6787023</v>
+        <v>6787043</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129367651</v>
+        <v>129367664</v>
       </c>
       <c r="B74" t="n">
         <v>79081</v>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>419250</v>
+        <v>419363</v>
       </c>
       <c r="R74" t="n">
-        <v>6787043</v>
+        <v>6787023</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129364490</v>
+        <v>129367662</v>
       </c>
       <c r="B81" t="n">
         <v>79081</v>
@@ -8604,17 +8604,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>419474</v>
+        <v>419339</v>
       </c>
       <c r="R81" t="n">
-        <v>6787027</v>
+        <v>6787019</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8658,19 +8658,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129367662</v>
+        <v>129364490</v>
       </c>
       <c r="B82" t="n">
         <v>79081</v>
@@ -8701,17 +8701,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>419339</v>
+        <v>419474</v>
       </c>
       <c r="R82" t="n">
-        <v>6787019</v>
+        <v>6787027</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8755,12 +8755,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129364474</v>
+        <v>129357097</v>
       </c>
       <c r="B86" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9069,21 +9069,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>419457</v>
+        <v>419496</v>
       </c>
       <c r="R86" t="n">
-        <v>6787068</v>
+        <v>6786922</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9143,19 +9143,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129357097</v>
+        <v>129367665</v>
       </c>
       <c r="B87" t="n">
         <v>79081</v>
@@ -9186,17 +9186,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, Dlr</t>
+          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>419496</v>
+        <v>419522</v>
       </c>
       <c r="R87" t="n">
-        <v>6786922</v>
+        <v>6786991</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9240,22 +9240,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129367665</v>
+        <v>129364474</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9263,37 +9263,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Säl-Hansbäckkojan, nordöst Sälen, Dlr</t>
+          <t>Säl-Hansbäckkojan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>419522</v>
+        <v>419457</v>
       </c>
       <c r="R88" t="n">
-        <v>6786991</v>
+        <v>6787068</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9337,12 +9337,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
